--- a/data/trans_orig/P21D3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir algún medicamento en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22878</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>45984</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13125</t>
+          <t>12635</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34532</t>
+          <t>35575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41151</t>
+          <t>40571</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>69102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>107705</t>
+          <t>108282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131388</t>
+          <t>131798</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91785</t>
+          <t>90742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113192</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>209262</t>
+          <t>211481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>239432</t>
+          <t>240012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33123</t>
+          <t>32189</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67396</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>36679</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60592</t>
+          <t>59740</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>76297</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>116908</t>
+          <t>118979</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141521</t>
+          <t>141177</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176692</t>
+          <t>177456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168411</t>
+          <t>169470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193116</t>
+          <t>193786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>321215</t>
+          <t>320327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363186</t>
+          <t>363977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>14890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17746</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33072</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60577</t>
+          <t>61219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62231</t>
+          <t>62740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78159</t>
+          <t>78127</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111914</t>
+          <t>111775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>127329</t>
+          <t>127221</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>179424</t>
+          <t>178433</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>201162</t>
+          <t>201824</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,93%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33943</t>
+          <t>34085</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>63875</t>
+          <t>62744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>64842</t>
+          <t>66950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188500</t>
+          <t>183714</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113157</t>
+          <t>113925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>270624</t>
+          <t>261105</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>77502</t>
+          <t>78633</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107434</t>
+          <t>107292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57545</t>
+          <t>62728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179841</t>
+          <t>177858</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117487</t>
+          <t>126270</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273383</t>
+          <t>273133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,41%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1696</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>14736</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>29612</t>
+          <t>30348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24345</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43398</t>
+          <t>43038</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>38669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>54260</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49648</t>
+          <t>50395</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61389</t>
+          <t>62006</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92887</t>
+          <t>91755</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111858</t>
+          <t>111809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,7%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10784</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12755</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>24568</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>42844</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28083</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>66691</t>
+          <t>68426</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81466</t>
+          <t>81753</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100278</t>
+          <t>100525</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82869</t>
+          <t>82162</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>96617</t>
+          <t>96395</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>168768</t>
+          <t>168398</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>193348</t>
+          <t>192654</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>64323</t>
+          <t>63666</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>103867</t>
+          <t>102994</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36273</t>
+          <t>36212</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62099</t>
+          <t>62926</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>108485</t>
+          <t>107671</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>155394</t>
+          <t>155754</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>205375</t>
+          <t>207127</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>245164</t>
+          <t>245913</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241509</t>
+          <t>241656</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>268089</t>
+          <t>268582</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>459610</t>
+          <t>456446</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>507158</t>
+          <t>505047</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7991</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>511</t>
+          <t>519</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4939</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3148</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>216786</t>
+          <t>214778</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>69843</t>
+          <t>68376</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>98757</t>
+          <t>97337</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>85703</t>
+          <t>93312</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>280787</t>
+          <t>281711</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>335264</t>
+          <t>337685</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>513314</t>
+          <t>518230</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>248356</t>
+          <t>250047</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>277225</t>
+          <t>279390</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>619056</t>
+          <t>617107</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>816001</t>
+          <t>808798</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>506</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>6649</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>243724</t>
+          <t>246203</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>490215</t>
+          <t>489607</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>307737</t>
+          <t>312466</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>562220</t>
+          <t>566321</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>623792</t>
+          <t>631918</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>945364</t>
+          <t>941522</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1164868</t>
+          <t>1165206</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1415592</t>
+          <t>1412086</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1010506</t>
+          <t>1011825</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1267577</t>
+          <t>1264713</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2292420</t>
+          <t>2297786</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2613632</t>
+          <t>2608184</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>16110</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32176</t>
+          <t>32824</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4438</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>614</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D3_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P21D3_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33686</t>
+          <t>39055</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22468</t>
+          <t>29458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45984</t>
+          <t>52474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>18869</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12635</t>
+          <t>12723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>28663</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53587</t>
+          <t>57924</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40571</t>
+          <t>44950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69102</t>
+          <t>74360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>120580</t>
+          <t>115232</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108282</t>
+          <t>101813</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131798</t>
+          <t>124829</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>65,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>106416</t>
+          <t>119840</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90742</t>
+          <t>110046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113682</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>226996</t>
+          <t>235072</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>211481</t>
+          <t>218636</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>240012</t>
+          <t>248046</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>154287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>280583</t>
+          <t>292996</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47486</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32189</t>
+          <t>35084</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>68675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47209</t>
+          <t>51002</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36679</t>
+          <t>39642</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59740</t>
+          <t>66229</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>94695</t>
+          <t>100917</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>76297</t>
+          <t>81425</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>118979</t>
+          <t>123560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>161795</t>
+          <t>169787</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141177</t>
+          <t>151826</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177456</t>
+          <t>185197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>182613</t>
+          <t>194161</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>169470</t>
+          <t>179182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193786</t>
+          <t>205957</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>344408</t>
+          <t>363948</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>320327</t>
+          <t>340586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363977</t>
+          <t>383830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>14793</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211273</t>
+          <t>221732</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>252716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>448554</t>
+          <t>474448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24176</t>
+          <t>23715</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>16424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33190</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>48877</t>
+          <t>48301</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37847</t>
+          <t>38364</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>61219</t>
+          <t>61645</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70736</t>
+          <t>69339</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62740</t>
+          <t>60987</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78127</t>
+          <t>76630</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,54%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>121194</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111775</t>
+          <t>112947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>127221</t>
+          <t>128101</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,22 +2046,22 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>191017</t>
+          <t>190533</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>178433</t>
+          <t>177663</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>201824</t>
+          <t>200482</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,74%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>560</t>
+          <t>561</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>145541</t>
+          <t>146342</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>240453</t>
+          <t>239396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47768</t>
+          <t>68048</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34085</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>62744</t>
+          <t>87478</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>120694</t>
+          <t>59312</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66950</t>
+          <t>47234</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183714</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>168462</t>
+          <t>127360</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>113925</t>
+          <t>105467</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261105</t>
+          <t>150376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>93609</t>
+          <t>106412</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>78633</t>
+          <t>86982</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107292</t>
+          <t>123745</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>124757</t>
+          <t>141032</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62728</t>
+          <t>127195</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177858</t>
+          <t>153261</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>63,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>218366</t>
+          <t>247444</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126270</t>
+          <t>223758</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273133</t>
+          <t>268700</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>141377</t>
+          <t>174460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>246560</t>
+          <t>201508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>387937</t>
+          <t>375968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14736</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30348</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>8625</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>20222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>42642</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>32902</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43038</t>
+          <t>53985</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>46758</t>
+          <t>52291</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>42446</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54260</t>
+          <t>60146</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>56572</t>
+          <t>61926</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50395</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62006</t>
+          <t>67493</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>103331</t>
+          <t>114218</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>91755</t>
+          <t>103698</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111809</t>
+          <t>124637</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>76,09%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13142</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>84421</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>71362</t>
+          <t>79385</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142066</t>
+          <t>163806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>34072</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>24568</t>
+          <t>24934</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>42844</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>15373</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>54171</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>68426</t>
+          <t>67525</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>91331</t>
+          <t>92027</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>81753</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>100525</t>
+          <t>101207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>90280</t>
+          <t>92464</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82162</t>
+          <t>84565</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>96395</t>
+          <t>98343</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>181611</t>
+          <t>184491</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>168398</t>
+          <t>172565</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>192654</t>
+          <t>196481</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>125594</t>
+          <t>126846</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>110952</t>
+          <t>113716</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>236546</t>
+          <t>240562</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>81859</t>
+          <t>87365</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>68648</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>102994</t>
+          <t>109751</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>53778</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>36212</t>
+          <t>41087</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>62926</t>
+          <t>68116</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>130326</t>
+          <t>141142</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>107671</t>
+          <t>117441</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>155754</t>
+          <t>169163</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>23,86%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>227636</t>
+          <t>263133</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>207127</t>
+          <t>241316</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>245913</t>
+          <t>281899</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>255919</t>
+          <t>299669</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>241656</t>
+          <t>285489</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>268582</t>
+          <t>312083</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>483554</t>
+          <t>562802</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>456446</t>
+          <t>534936</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>505047</t>
+          <t>586237</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4375,12 +4375,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5465</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>311736</t>
+          <t>352807</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>306854</t>
+          <t>356179</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>708986</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>115198</t>
+          <t>141466</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>121515</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>214778</t>
+          <t>162359</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>102426</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>68376</t>
+          <t>87500</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>97337</t>
+          <t>120780</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>197620</t>
+          <t>243892</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>93312</t>
+          <t>215581</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>281711</t>
+          <t>270665</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>438010</t>
+          <t>218480</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>337685</t>
+          <t>198793</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>518230</t>
+          <t>239104</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>265010</t>
+          <t>304036</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>250047</t>
+          <t>285970</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>279390</t>
+          <t>319213</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>703019</t>
+          <t>522516</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>617107</t>
+          <t>495311</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>808798</t>
+          <t>551078</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>721</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>593</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>553916</t>
+          <t>360667</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>349107</t>
+          <t>408379</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>903023</t>
+          <t>769046</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>405056</t>
+          <t>473086</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>246203</t>
+          <t>429964</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>489607</t>
+          <t>518785</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>375123</t>
+          <t>344416</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>312466</t>
+          <t>312930</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>566321</t>
+          <t>375775</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>780179</t>
+          <t>817503</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>631918</t>
+          <t>766603</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>941522</t>
+          <t>869858</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1250455</t>
+          <t>1086701</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1165206</t>
+          <t>1041293</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1412086</t>
+          <t>1129936</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1201847</t>
+          <t>1334324</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1011825</t>
+          <t>1302634</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1264713</t>
+          <t>1366730</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2452303</t>
+          <t>2421025</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2297786</t>
+          <t>2367854</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2608184</t>
+          <t>2473655</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>7502</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>14990</t>
+          <t>16183</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>21991</t>
+          <t>25321</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>16527</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>34179</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,17 +5656,17 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>564</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,22 +5686,22 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
